--- a/results/ghg_emissions_co2e_2025.xlsx
+++ b/results/ghg_emissions_co2e_2025.xlsx
@@ -4739,10 +4739,10 @@
         <v>4.64542533</v>
       </c>
       <c r="E211" t="n">
-        <v>7.74932583333333</v>
+        <v>7.74368996</v>
       </c>
       <c r="F211" t="n">
-        <v>8.86113360823409</v>
+        <v>8.8546891474281</v>
       </c>
     </row>
     <row r="212">
@@ -4759,10 +4759,10 @@
         <v>4.778113545</v>
       </c>
       <c r="E212" t="n">
-        <v>6.71088916666667</v>
+        <v>6.70600852</v>
       </c>
       <c r="F212" t="n">
-        <v>9.39384229339963</v>
+        <v>9.38701040809534</v>
       </c>
     </row>
     <row r="213">
@@ -4779,10 +4779,10 @@
         <v>4.819597776</v>
       </c>
       <c r="E213" t="n">
-        <v>6.82549083333333</v>
+        <v>6.82052684</v>
       </c>
       <c r="F213" t="n">
-        <v>9.42189442332347</v>
+        <v>9.41504213647015</v>
       </c>
     </row>
     <row r="214">
@@ -4799,10 +4799,10 @@
         <v>4.89627423</v>
       </c>
       <c r="E214" t="n">
-        <v>6.33530333333333</v>
+        <v>6.33069584</v>
       </c>
       <c r="F214" t="n">
-        <v>9.75438125975973</v>
+        <v>9.74728716429809</v>
       </c>
     </row>
     <row r="215">
@@ -4819,10 +4819,10 @@
         <v>5.014258029</v>
       </c>
       <c r="E215" t="n">
-        <v>6.16576583333333</v>
+        <v>6.16128164</v>
       </c>
       <c r="F215" t="n">
-        <v>10.274244391324</v>
+        <v>10.2667722135849</v>
       </c>
     </row>
     <row r="216">
@@ -4839,10 +4839,10 @@
         <v>5.112300861</v>
       </c>
       <c r="E216" t="n">
-        <v>5.86309166666667</v>
+        <v>5.8588276</v>
       </c>
       <c r="F216" t="n">
-        <v>10.832344166335</v>
+        <v>10.8244660978504</v>
       </c>
     </row>
     <row r="217">
@@ -4859,10 +4859,10 @@
         <v>5.244749973</v>
       </c>
       <c r="E217" t="n">
-        <v>5.629195</v>
+        <v>5.62510104</v>
       </c>
       <c r="F217" t="n">
-        <v>11.3188323198998</v>
+        <v>11.3106004418489</v>
       </c>
     </row>
     <row r="218">
@@ -4879,10 +4879,10 @@
         <v>5.438582991</v>
       </c>
       <c r="E218" t="n">
-        <v>5.22663166666667</v>
+        <v>5.22283048</v>
       </c>
       <c r="F218" t="n">
-        <v>11.8712799822229</v>
+        <v>11.8626463240541</v>
       </c>
     </row>
     <row r="219">
@@ -4899,10 +4899,10 @@
         <v>5.501685258</v>
       </c>
       <c r="E219" t="n">
-        <v>5.40478583333333</v>
+        <v>5.40085508</v>
       </c>
       <c r="F219" t="n">
-        <v>12.2462756580096</v>
+        <v>12.2373692757128</v>
       </c>
     </row>
     <row r="220">
@@ -4919,10 +4919,10 @@
         <v>5.593461471</v>
       </c>
       <c r="E220" t="n">
-        <v>5.33628333333333</v>
+        <v>5.3324024</v>
       </c>
       <c r="F220" t="n">
-        <v>12.914675562988</v>
+        <v>12.9052830716695</v>
       </c>
     </row>
     <row r="221">
@@ -4939,10 +4939,10 @@
         <v>5.765987817</v>
       </c>
       <c r="E221" t="n">
-        <v>5.84022083333333</v>
+        <v>5.8359734</v>
       </c>
       <c r="F221" t="n">
-        <v>13.7718011439915</v>
+        <v>13.7617852886141</v>
       </c>
     </row>
     <row r="222">
@@ -4959,10 +4959,10 @@
         <v>5.913418392</v>
       </c>
       <c r="E222" t="n">
-        <v>5.6982475</v>
+        <v>5.69410332</v>
       </c>
       <c r="F222" t="n">
-        <v>14.9099680504149</v>
+        <v>14.8991244372874</v>
       </c>
     </row>
     <row r="223">
@@ -4979,10 +4979,10 @@
         <v>5.931506799</v>
       </c>
       <c r="E223" t="n">
-        <v>5.12182</v>
+        <v>5.11809504</v>
       </c>
       <c r="F223" t="n">
-        <v>15.5151384539614</v>
+        <v>15.503854716904</v>
       </c>
     </row>
     <row r="224">
@@ -4999,10 +4999,10 @@
         <v>6.055044372</v>
       </c>
       <c r="E224" t="n">
-        <v>5.3944825</v>
+        <v>5.39055924</v>
       </c>
       <c r="F224" t="n">
-        <v>16.2364049445817</v>
+        <v>16.2245966500765</v>
       </c>
     </row>
     <row r="225">
@@ -5019,10 +5019,10 @@
         <v>6.209755731</v>
       </c>
       <c r="E225" t="n">
-        <v>5.24789833333333</v>
+        <v>5.24408168</v>
       </c>
       <c r="F225" t="n">
-        <v>17.0975274636657</v>
+        <v>17.0850928982376</v>
       </c>
     </row>
     <row r="226">
@@ -5039,10 +5039,10 @@
         <v>6.229990764</v>
       </c>
       <c r="E226" t="n">
-        <v>5.1421425</v>
+        <v>5.13840276</v>
       </c>
       <c r="F226" t="n">
-        <v>17.0234523753271</v>
+        <v>17.0110716826905</v>
       </c>
     </row>
     <row r="227">
@@ -5059,10 +5059,10 @@
         <v>6.315886215</v>
       </c>
       <c r="E227" t="n">
-        <v>5.06301583333333</v>
+        <v>5.05933364</v>
       </c>
       <c r="F227" t="n">
-        <v>17.0651636542993</v>
+        <v>17.0527526261871</v>
       </c>
     </row>
     <row r="228">
@@ -5079,10 +5079,10 @@
         <v>6.408602937</v>
       </c>
       <c r="E228" t="n">
-        <v>5.08787583333333</v>
+        <v>5.08417556</v>
       </c>
       <c r="F228" t="n">
-        <v>18.0022045783997</v>
+        <v>17.989112065979</v>
       </c>
     </row>
     <row r="229">
@@ -5099,10 +5099,10 @@
         <v>6.488835525</v>
       </c>
       <c r="E229" t="n">
-        <v>5.51778333333333</v>
+        <v>5.5137704</v>
       </c>
       <c r="F229" t="n">
-        <v>18.5120975602936</v>
+        <v>18.4986342166133</v>
       </c>
     </row>
     <row r="230">
@@ -5119,10 +5119,10 @@
         <v>6.515872857</v>
       </c>
       <c r="E230" t="n">
-        <v>5.41699583333333</v>
+        <v>5.4130562</v>
       </c>
       <c r="F230" t="n">
-        <v>19.0831692081967</v>
+        <v>19.0692905396817</v>
       </c>
     </row>
     <row r="231">
@@ -5139,10 +5139,10 @@
         <v>6.677913546</v>
       </c>
       <c r="E231" t="n">
-        <v>4.69016166666667</v>
+        <v>4.68675064</v>
       </c>
       <c r="F231" t="n">
-        <v>19.6232917764951</v>
+        <v>19.6090202915667</v>
       </c>
     </row>
     <row r="232">
@@ -5159,10 +5159,10 @@
         <v>6.644636379</v>
       </c>
       <c r="E232" t="n">
-        <v>4.9711475</v>
+        <v>4.96753212</v>
       </c>
       <c r="F232" t="n">
-        <v>19.5027081969085</v>
+        <v>19.4885244091289</v>
       </c>
     </row>
     <row r="233">
@@ -5179,10 +5179,10 @@
         <v>6.47861994</v>
       </c>
       <c r="E233" t="n">
-        <v>4.833455</v>
+        <v>4.82993976</v>
       </c>
       <c r="F233" t="n">
-        <v>19.0367496894457</v>
+        <v>19.0229047805807</v>
       </c>
     </row>
     <row r="234">
@@ -5199,10 +5199,10 @@
         <v>6.550706286</v>
       </c>
       <c r="E234" t="n">
-        <v>4.54700583333333</v>
+        <v>4.54369892</v>
       </c>
       <c r="F234" t="n">
-        <v>18.8848323301712</v>
+        <v>18.8710979066584</v>
       </c>
     </row>
     <row r="235">
@@ -5219,10 +5219,10 @@
         <v>6.551675532</v>
       </c>
       <c r="E235" t="n">
-        <v>4.7884375</v>
+        <v>4.784955</v>
       </c>
       <c r="F235" t="n">
-        <v>19.0057327840849</v>
+        <v>18.9919104329692</v>
       </c>
     </row>
     <row r="236">
@@ -5239,10 +5239,10 @@
         <v>6.629444829</v>
       </c>
       <c r="E236" t="n">
-        <v>5.64318333333333</v>
+        <v>5.6390792</v>
       </c>
       <c r="F236" t="n">
-        <v>19.6621011296009</v>
+        <v>19.6478014196884</v>
       </c>
     </row>
     <row r="237">
@@ -5259,10 +5259,10 @@
         <v>6.715913625</v>
       </c>
       <c r="E237" t="n">
-        <v>5.29481333333333</v>
+        <v>5.29096256</v>
       </c>
       <c r="F237" t="n">
-        <v>20.3266846689902</v>
+        <v>20.3119016255946</v>
       </c>
     </row>
     <row r="238">
@@ -5279,10 +5279,10 @@
         <v>6.796219869</v>
       </c>
       <c r="E238" t="n">
-        <v>5.53120333333333</v>
+        <v>5.52718064</v>
       </c>
       <c r="F238" t="n">
-        <v>20.6299668036197</v>
+        <v>20.6149631913989</v>
       </c>
     </row>
     <row r="239">
@@ -5299,10 +5299,10 @@
         <v>6.854532822</v>
       </c>
       <c r="E239" t="n">
-        <v>5.34369</v>
+        <v>5.33980368</v>
       </c>
       <c r="F239" t="n">
-        <v>21.2655404490995</v>
+        <v>21.2500746015001</v>
       </c>
     </row>
     <row r="240">
@@ -5319,10 +5319,10 @@
         <v>6.959527776</v>
       </c>
       <c r="E240" t="n">
-        <v>5.17474833333333</v>
+        <v>5.17098488</v>
       </c>
       <c r="F240" t="n">
-        <v>22.1012036142456</v>
+        <v>22.085130011617</v>
       </c>
     </row>
     <row r="241">
@@ -5339,10 +5339,10 @@
         <v>7.113117834</v>
       </c>
       <c r="E241" t="n">
-        <v>4.95694833333333</v>
+        <v>4.95334328</v>
       </c>
       <c r="F241" t="n">
-        <v>22.402930515263</v>
+        <v>22.3866374748882</v>
       </c>
     </row>
     <row r="242">
@@ -5359,10 +5359,10 @@
         <v>7.162078428</v>
       </c>
       <c r="E242" t="n">
-        <v>4.9802225</v>
+        <v>4.97660052</v>
       </c>
       <c r="F242" t="n">
-        <v>22.7455305016103</v>
+        <v>22.7289882976092</v>
       </c>
     </row>
     <row r="243">
@@ -5379,10 +5379,10 @@
         <v>7.110473193</v>
       </c>
       <c r="E243" t="n">
-        <v>4.97360416666667</v>
+        <v>4.969987</v>
       </c>
       <c r="F243" t="n">
-        <v>23.2029763350841</v>
+        <v>23.186101443204</v>
       </c>
     </row>
     <row r="244">
@@ -5399,10 +5399,10 @@
         <v>7.111760778</v>
       </c>
       <c r="E244" t="n">
-        <v>5.26183166666667</v>
+        <v>5.25800488</v>
       </c>
       <c r="F244" t="n">
-        <v>22.5445680820615</v>
+        <v>22.5281720325473</v>
       </c>
     </row>
     <row r="245">
@@ -5419,10 +5419,10 @@
         <v>7.103548134</v>
       </c>
       <c r="E245" t="n">
-        <v>4.97748166666667</v>
+        <v>4.97386168</v>
       </c>
       <c r="F245" t="n">
-        <v>22.7723486928004</v>
+        <v>22.7557869846602</v>
       </c>
     </row>
     <row r="246">
@@ -5439,10 +5439,10 @@
         <v>7.17585489</v>
       </c>
       <c r="E246" t="n">
-        <v>5.8936625</v>
+        <v>5.8893762</v>
       </c>
       <c r="F246" t="n">
-        <v>23.0096812121402</v>
+        <v>22.9929468985314</v>
       </c>
     </row>
     <row r="247">
@@ -5459,10 +5459,10 @@
         <v>7.261683381</v>
       </c>
       <c r="E247" t="n">
-        <v>5.43635583333333</v>
+        <v>5.43240212</v>
       </c>
       <c r="F247" t="n">
-        <v>23.5492097041488</v>
+        <v>23.5320830061822</v>
       </c>
     </row>
     <row r="248">
@@ -5479,10 +5479,10 @@
         <v>7.342554042</v>
       </c>
       <c r="E248" t="n">
-        <v>6.0169175</v>
+        <v>6.01254156</v>
       </c>
       <c r="F248" t="n">
-        <v>24.2758225927639</v>
+        <v>24.25816744906</v>
       </c>
     </row>
     <row r="249">
@@ -5499,10 +5499,10 @@
         <v>7.312412835</v>
       </c>
       <c r="E249" t="n">
-        <v>7.41195583333333</v>
+        <v>7.40656532</v>
       </c>
       <c r="F249" t="n">
-        <v>24.419665462057</v>
+        <v>24.4019057053573</v>
       </c>
     </row>
     <row r="250">
@@ -5519,10 +5519,10 @@
         <v>7.252801416</v>
       </c>
       <c r="E250" t="n">
-        <v>6.14893583333333</v>
+        <v>6.14446388</v>
       </c>
       <c r="F250" t="n">
-        <v>24.3214656529147</v>
+        <v>24.303777314258</v>
       </c>
     </row>
     <row r="251">
@@ -5539,10 +5539,10 @@
         <v>7.271589276</v>
       </c>
       <c r="E251" t="n">
-        <v>6.00728333333333</v>
+        <v>6.0029144</v>
       </c>
       <c r="F251" t="n">
-        <v>24.871816272449</v>
+        <v>24.8537276787963</v>
       </c>
     </row>
     <row r="252">
@@ -5559,10 +5559,10 @@
         <v>7.373737035</v>
       </c>
       <c r="E252" t="n">
-        <v>5.30107416666667</v>
+        <v>5.29721884</v>
       </c>
       <c r="F252" t="n">
-        <v>25.5291194291589</v>
+        <v>25.5105527968468</v>
       </c>
     </row>
     <row r="253">
@@ -5579,10 +5579,10 @@
         <v>7.353559476</v>
       </c>
       <c r="E253" t="n">
-        <v>4.76871083333333</v>
+        <v>4.76524268</v>
       </c>
       <c r="F253" t="n">
-        <v>25.7250025403732</v>
+        <v>25.7062934476166</v>
       </c>
     </row>
     <row r="254">
@@ -5599,10 +5599,10 @@
         <v>7.315330896</v>
       </c>
       <c r="E254" t="n">
-        <v>5.13184833333333</v>
+        <v>5.12811608</v>
       </c>
       <c r="F254" t="n">
-        <v>26.2959930870007</v>
+        <v>26.276868728392</v>
       </c>
     </row>
     <row r="255">
@@ -5610,7 +5610,7 @@
         <v>2003</v>
       </c>
       <c r="B255" t="n">
-        <v>0.776640464399668</v>
+        <v>0.780403881718558</v>
       </c>
       <c r="C255" t="n">
         <v>2.419630122</v>
@@ -5619,10 +5619,10 @@
         <v>7.491286431</v>
       </c>
       <c r="E255" t="n">
-        <v>6.08010333333333</v>
+        <v>6.07568144</v>
       </c>
       <c r="F255" t="n">
-        <v>27.6896277003213</v>
+        <v>27.6694897892665</v>
       </c>
     </row>
     <row r="256">
@@ -5630,7 +5630,7 @@
         <v>2004</v>
       </c>
       <c r="B256" t="n">
-        <v>0.834665285648973</v>
+        <v>0.836287884470271</v>
       </c>
       <c r="C256" t="n">
         <v>2.4880422021</v>
@@ -5639,10 +5639,10 @@
         <v>7.627832658</v>
       </c>
       <c r="E256" t="n">
-        <v>5.40792083333333</v>
+        <v>5.4039878</v>
       </c>
       <c r="F256" t="n">
-        <v>28.6533447255843</v>
+        <v>28.6325059294202</v>
       </c>
     </row>
     <row r="257">
@@ -5650,7 +5650,7 @@
         <v>2005</v>
       </c>
       <c r="B257" t="n">
-        <v>0.888070284953287</v>
+        <v>0.882154018450314</v>
       </c>
       <c r="C257" t="n">
         <v>2.5104898728</v>
@@ -5659,10 +5659,10 @@
         <v>7.743612636</v>
       </c>
       <c r="E257" t="n">
-        <v>4.89454166666667</v>
+        <v>4.890982</v>
       </c>
       <c r="F257" t="n">
-        <v>29.6359475157134</v>
+        <v>29.6143940993383</v>
       </c>
     </row>
     <row r="258">
@@ -5670,7 +5670,7 @@
         <v>2006</v>
       </c>
       <c r="B258" t="n">
-        <v>0.934406054407556</v>
+        <v>0.934501799384499</v>
       </c>
       <c r="C258" t="n">
         <v>2.5465334895</v>
@@ -5679,10 +5679,10 @@
         <v>7.866271359</v>
       </c>
       <c r="E258" t="n">
-        <v>5.33602666666667</v>
+        <v>5.33214592</v>
       </c>
       <c r="F258" t="n">
-        <v>30.6506875104364</v>
+        <v>30.6283961013379</v>
       </c>
     </row>
     <row r="259">
@@ -5690,7 +5690,7 @@
         <v>2007</v>
       </c>
       <c r="B259" t="n">
-        <v>0.963402088309819</v>
+        <v>0.96747443301657</v>
       </c>
       <c r="C259" t="n">
         <v>2.6131911351</v>
@@ -5699,10 +5699,10 @@
         <v>7.916794353</v>
       </c>
       <c r="E259" t="n">
-        <v>4.59792666666667</v>
+        <v>4.59458272</v>
       </c>
       <c r="F259" t="n">
-        <v>31.5575950085711</v>
+        <v>31.534644030383</v>
       </c>
     </row>
     <row r="260">
@@ -5710,7 +5710,7 @@
         <v>2008</v>
       </c>
       <c r="B260" t="n">
-        <v>0.973156170270452</v>
+        <v>0.970192400628376</v>
       </c>
       <c r="C260" t="n">
         <v>2.583179235</v>
@@ -5719,10 +5719,10 @@
         <v>7.98296283</v>
       </c>
       <c r="E260" t="n">
-        <v>4.8838625</v>
+        <v>4.8803106</v>
       </c>
       <c r="F260" t="n">
-        <v>32.0975422275036</v>
+        <v>32.0741985604291</v>
       </c>
     </row>
     <row r="261">
@@ -5730,7 +5730,7 @@
         <v>2009</v>
       </c>
       <c r="B261" t="n">
-        <v>0.988830357466841</v>
+        <v>0.986469931986331</v>
       </c>
       <c r="C261" t="n">
         <v>2.5529533302</v>
@@ -5739,10 +5739,10 @@
         <v>7.9322769</v>
       </c>
       <c r="E261" t="n">
-        <v>5.27781833333333</v>
+        <v>5.27397992</v>
       </c>
       <c r="F261" t="n">
-        <v>31.5648782181915</v>
+        <v>31.5419219431237</v>
       </c>
     </row>
     <row r="262">
@@ -5750,7 +5750,7 @@
         <v>2010</v>
       </c>
       <c r="B262" t="n">
-        <v>1.05774181127664</v>
+        <v>1.05824870034321</v>
       </c>
       <c r="C262" t="n">
         <v>2.6176142811</v>
@@ -5759,10 +5759,10 @@
         <v>8.058531096</v>
       </c>
       <c r="E262" t="n">
-        <v>5.49190583333333</v>
+        <v>5.48791172</v>
       </c>
       <c r="F262" t="n">
-        <v>33.3801799370199</v>
+        <v>33.3559034425203</v>
       </c>
     </row>
     <row r="263">
@@ -5770,7 +5770,7 @@
         <v>2011</v>
       </c>
       <c r="B263" t="n">
-        <v>1.13355529207935</v>
+        <v>1.13455992991747</v>
       </c>
       <c r="C263" t="n">
         <v>2.7033335511</v>
@@ -5779,10 +5779,10 @@
         <v>8.289513801</v>
       </c>
       <c r="E263" t="n">
-        <v>5.28210833333333</v>
+        <v>5.2782668</v>
       </c>
       <c r="F263" t="n">
-        <v>34.5296505924255</v>
+        <v>34.5045381192674</v>
       </c>
     </row>
     <row r="264">
@@ -5790,7 +5790,7 @@
         <v>2012</v>
       </c>
       <c r="B264" t="n">
-        <v>1.20677886438571</v>
+        <v>1.2089277631022</v>
       </c>
       <c r="C264" t="n">
         <v>2.7177094035</v>
@@ -5799,10 +5799,10 @@
         <v>8.356626414</v>
       </c>
       <c r="E264" t="n">
-        <v>5.6560075</v>
+        <v>5.65189404</v>
       </c>
       <c r="F264" t="n">
-        <v>35.025493429272</v>
+        <v>35.0000203431416</v>
       </c>
     </row>
     <row r="265">
@@ -5810,7 +5810,7 @@
         <v>2013</v>
       </c>
       <c r="B265" t="n">
-        <v>1.28582066166584</v>
+        <v>1.28544290079567</v>
       </c>
       <c r="C265" t="n">
         <v>2.7006362292</v>
@@ -5819,10 +5819,10 @@
         <v>8.308616652</v>
       </c>
       <c r="E265" t="n">
-        <v>5.11987666666667</v>
+        <v>5.11615312</v>
       </c>
       <c r="F265" t="n">
-        <v>35.3273484616819</v>
+        <v>35.3016558446189</v>
       </c>
     </row>
     <row r="266">
@@ -5830,7 +5830,7 @@
         <v>2014</v>
       </c>
       <c r="B266" t="n">
-        <v>1.35030131892773</v>
+        <v>1.33444992243006</v>
       </c>
       <c r="C266" t="n">
         <v>2.734247334</v>
@@ -5839,10 +5839,10 @@
         <v>8.386863039</v>
       </c>
       <c r="E266" t="n">
-        <v>5.40012</v>
+        <v>5.39619264</v>
       </c>
       <c r="F266" t="n">
-        <v>35.4758953972387</v>
+        <v>35.4500947460407</v>
       </c>
     </row>
     <row r="267">
@@ -5850,7 +5850,7 @@
         <v>2015</v>
       </c>
       <c r="B267" t="n">
-        <v>1.40939801279057</v>
+        <v>1.40251443216763</v>
       </c>
       <c r="C267" t="n">
         <v>2.74165983</v>
@@ -5859,10 +5859,10 @@
         <v>8.401728438</v>
       </c>
       <c r="E267" t="n">
-        <v>5.5356125</v>
+        <v>5.5315866</v>
       </c>
       <c r="F267" t="n">
-        <v>35.4306647269067</v>
+        <v>35.4048969707417</v>
       </c>
     </row>
     <row r="268">
@@ -5870,7 +5870,7 @@
         <v>2016</v>
       </c>
       <c r="B268" t="n">
-        <v>1.4970701359135</v>
+        <v>1.50776506934997</v>
       </c>
       <c r="C268" t="n">
         <v>2.759551704</v>
@@ -5879,10 +5879,10 @@
         <v>8.438158305</v>
       </c>
       <c r="E268" t="n">
-        <v>4.40946</v>
+        <v>4.40625312</v>
       </c>
       <c r="F268" t="n">
-        <v>35.4424323905176</v>
+        <v>35.4166560760518</v>
       </c>
     </row>
     <row r="269">
@@ -5890,7 +5890,7 @@
         <v>2017</v>
       </c>
       <c r="B269" t="n">
-        <v>1.60073843634916</v>
+        <v>1.60821184549608</v>
       </c>
       <c r="C269" t="n">
         <v>2.815031037</v>
@@ -5899,10 +5899,10 @@
         <v>8.576309898</v>
       </c>
       <c r="E269" t="n">
-        <v>4.23410166666667</v>
+        <v>4.23102232</v>
       </c>
       <c r="F269" t="n">
-        <v>36.0160913972762</v>
+        <v>35.98989787626</v>
       </c>
     </row>
     <row r="270">
@@ -5910,7 +5910,7 @@
         <v>2018</v>
       </c>
       <c r="B270" t="n">
-        <v>1.67457814197597</v>
+        <v>1.68435257202591</v>
       </c>
       <c r="C270" t="n">
         <v>2.814308679</v>
@@ -5919,10 +5919,10 @@
         <v>8.705310849</v>
       </c>
       <c r="E270" t="n">
-        <v>3.84751583333333</v>
+        <v>3.84471764</v>
       </c>
       <c r="F270" t="n">
-        <v>36.7571590366622</v>
+        <v>36.7304265573628</v>
       </c>
     </row>
     <row r="271">
@@ -5930,7 +5930,7 @@
         <v>2019</v>
       </c>
       <c r="B271" t="n">
-        <v>1.69678141919574</v>
+        <v>1.73907398402602</v>
       </c>
       <c r="C271" t="n">
         <v>2.819371737</v>
@@ -5939,10 +5939,10 @@
         <v>8.77280067</v>
       </c>
       <c r="E271" t="n">
-        <v>3.7895</v>
+        <v>3.786744</v>
       </c>
       <c r="F271" t="n">
-        <v>37.1312824268496</v>
+        <v>37.1042778578119</v>
       </c>
     </row>
     <row r="272">
@@ -5950,7 +5950,7 @@
         <v>2020</v>
       </c>
       <c r="B272" t="n">
-        <v>1.74437453991104</v>
+        <v>1.78725447483064</v>
       </c>
       <c r="C272" t="n">
         <v>2.853203808</v>
@@ -5959,10 +5959,10 @@
         <v>8.67860748</v>
       </c>
       <c r="E272" t="n">
-        <v>3.44149666666667</v>
+        <v>3.43899376</v>
       </c>
       <c r="F272" t="n">
-        <v>35.1520912810263</v>
+        <v>35.126526123731</v>
       </c>
     </row>
     <row r="273">
@@ -5970,7 +5970,7 @@
         <v>2021</v>
       </c>
       <c r="B273" t="n">
-        <v>1.83923064254963</v>
+        <v>1.84120328472431</v>
       </c>
       <c r="C273" t="n">
         <v>2.895777339</v>
@@ -5979,10 +5979,10 @@
         <v>8.855243775</v>
       </c>
       <c r="E273" t="n">
-        <v>3.555365</v>
+        <v>3.55277928</v>
       </c>
       <c r="F273" t="n">
-        <v>37.0186589367089</v>
+        <v>36.991736275664</v>
       </c>
     </row>
     <row r="274">
@@ -5990,7 +5990,7 @@
         <v>2022</v>
       </c>
       <c r="B274" t="n">
-        <v>1.80775209790979</v>
+        <v>1.82284668679798</v>
       </c>
       <c r="C274" t="n">
         <v>2.882097582</v>
@@ -5999,10 +5999,10 @@
         <v>9.034107885</v>
       </c>
       <c r="E274" t="n">
-        <v>3.54361333333333</v>
+        <v>3.54103616</v>
       </c>
       <c r="F274" t="n">
-        <v>37.3209789229002</v>
+        <v>37.2938363927745</v>
       </c>
     </row>
     <row r="275">
@@ -6010,7 +6010,7 @@
         <v>2023</v>
       </c>
       <c r="B275" t="n">
-        <v>1.81745276436777</v>
+        <v>1.5696262934027</v>
       </c>
       <c r="C275" t="n">
         <v>2.912036946</v>
@@ -6019,10 +6019,10 @@
         <v>9.164639988</v>
       </c>
       <c r="E275" t="n">
-        <v>3.62754333333333</v>
+        <v>3.62490512</v>
       </c>
       <c r="F275" t="n">
-        <v>37.8190734917461</v>
+        <v>37.7915687110248</v>
       </c>
     </row>
   </sheetData>
@@ -6067,7 +6067,7 @@
         <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>8.86113360823409</v>
+        <v>8.8546891474281</v>
       </c>
     </row>
     <row r="3">
@@ -6084,7 +6084,7 @@
         <v>28</v>
       </c>
       <c r="E3" t="n">
-        <v>9.39384229339963</v>
+        <v>9.38701040809534</v>
       </c>
     </row>
     <row r="4">
@@ -6101,7 +6101,7 @@
         <v>29</v>
       </c>
       <c r="E4" t="n">
-        <v>9.42189442332347</v>
+        <v>9.41504213647015</v>
       </c>
     </row>
     <row r="5">
@@ -6118,7 +6118,7 @@
         <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>9.75438125975973</v>
+        <v>9.74728716429809</v>
       </c>
     </row>
     <row r="6">
@@ -6135,7 +6135,7 @@
         <v>31</v>
       </c>
       <c r="E6" t="n">
-        <v>10.274244391324</v>
+        <v>10.2667722135849</v>
       </c>
     </row>
     <row r="7">
@@ -6152,7 +6152,7 @@
         <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>10.832344166335</v>
+        <v>10.8244660978504</v>
       </c>
     </row>
     <row r="8">
@@ -6169,7 +6169,7 @@
         <v>33</v>
       </c>
       <c r="E8" t="n">
-        <v>11.3188323198998</v>
+        <v>11.3106004418489</v>
       </c>
     </row>
     <row r="9">
@@ -6186,7 +6186,7 @@
         <v>34</v>
       </c>
       <c r="E9" t="n">
-        <v>11.8712799822229</v>
+        <v>11.8626463240541</v>
       </c>
     </row>
     <row r="10">
@@ -6203,7 +6203,7 @@
         <v>35</v>
       </c>
       <c r="E10" t="n">
-        <v>12.2462756580096</v>
+        <v>12.2373692757128</v>
       </c>
     </row>
     <row r="11">
@@ -6220,7 +6220,7 @@
         <v>36</v>
       </c>
       <c r="E11" t="n">
-        <v>12.914675562988</v>
+        <v>12.9052830716695</v>
       </c>
     </row>
     <row r="12">
@@ -6237,7 +6237,7 @@
         <v>37</v>
       </c>
       <c r="E12" t="n">
-        <v>13.7718011439915</v>
+        <v>13.7617852886141</v>
       </c>
     </row>
     <row r="13">
@@ -6254,7 +6254,7 @@
         <v>38</v>
       </c>
       <c r="E13" t="n">
-        <v>14.9099680504149</v>
+        <v>14.8991244372874</v>
       </c>
     </row>
     <row r="14">
@@ -6271,7 +6271,7 @@
         <v>39</v>
       </c>
       <c r="E14" t="n">
-        <v>15.5151384539614</v>
+        <v>15.503854716904</v>
       </c>
     </row>
     <row r="15">
@@ -6288,7 +6288,7 @@
         <v>40</v>
       </c>
       <c r="E15" t="n">
-        <v>16.2364049445817</v>
+        <v>16.2245966500765</v>
       </c>
     </row>
     <row r="16">
@@ -6305,7 +6305,7 @@
         <v>41</v>
       </c>
       <c r="E16" t="n">
-        <v>17.0975274636657</v>
+        <v>17.0850928982376</v>
       </c>
     </row>
     <row r="17">
@@ -6322,7 +6322,7 @@
         <v>42</v>
       </c>
       <c r="E17" t="n">
-        <v>17.0234523753271</v>
+        <v>17.0110716826905</v>
       </c>
     </row>
     <row r="18">
@@ -6339,7 +6339,7 @@
         <v>43</v>
       </c>
       <c r="E18" t="n">
-        <v>17.0651636542993</v>
+        <v>17.0527526261871</v>
       </c>
     </row>
     <row r="19">
@@ -6356,7 +6356,7 @@
         <v>44</v>
       </c>
       <c r="E19" t="n">
-        <v>18.0022045783997</v>
+        <v>17.989112065979</v>
       </c>
     </row>
     <row r="20">
@@ -6373,7 +6373,7 @@
         <v>45</v>
       </c>
       <c r="E20" t="n">
-        <v>18.5120975602936</v>
+        <v>18.4986342166133</v>
       </c>
     </row>
     <row r="21">
@@ -6390,7 +6390,7 @@
         <v>46</v>
       </c>
       <c r="E21" t="n">
-        <v>19.0831692081967</v>
+        <v>19.0692905396817</v>
       </c>
     </row>
     <row r="22">
@@ -6407,7 +6407,7 @@
         <v>47</v>
       </c>
       <c r="E22" t="n">
-        <v>19.6232917764951</v>
+        <v>19.6090202915667</v>
       </c>
     </row>
     <row r="23">
@@ -6424,7 +6424,7 @@
         <v>48</v>
       </c>
       <c r="E23" t="n">
-        <v>19.5027081969085</v>
+        <v>19.4885244091289</v>
       </c>
     </row>
     <row r="24">
@@ -6441,7 +6441,7 @@
         <v>49</v>
       </c>
       <c r="E24" t="n">
-        <v>19.0367496894457</v>
+        <v>19.0229047805807</v>
       </c>
     </row>
     <row r="25">
@@ -6458,7 +6458,7 @@
         <v>50</v>
       </c>
       <c r="E25" t="n">
-        <v>18.8848323301712</v>
+        <v>18.8710979066584</v>
       </c>
     </row>
     <row r="26">
@@ -6475,7 +6475,7 @@
         <v>51</v>
       </c>
       <c r="E26" t="n">
-        <v>19.0057327840849</v>
+        <v>18.9919104329692</v>
       </c>
     </row>
     <row r="27">
@@ -6492,7 +6492,7 @@
         <v>52</v>
       </c>
       <c r="E27" t="n">
-        <v>19.6621011296009</v>
+        <v>19.6478014196884</v>
       </c>
     </row>
     <row r="28">
@@ -6509,7 +6509,7 @@
         <v>53</v>
       </c>
       <c r="E28" t="n">
-        <v>20.3266846689902</v>
+        <v>20.3119016255946</v>
       </c>
     </row>
     <row r="29">
@@ -6526,7 +6526,7 @@
         <v>54</v>
       </c>
       <c r="E29" t="n">
-        <v>20.6299668036197</v>
+        <v>20.6149631913989</v>
       </c>
     </row>
     <row r="30">
@@ -6543,7 +6543,7 @@
         <v>55</v>
       </c>
       <c r="E30" t="n">
-        <v>21.2655404490995</v>
+        <v>21.2500746015001</v>
       </c>
     </row>
     <row r="31">
@@ -6560,7 +6560,7 @@
         <v>56</v>
       </c>
       <c r="E31" t="n">
-        <v>22.1012036142456</v>
+        <v>22.085130011617</v>
       </c>
     </row>
     <row r="32">
@@ -6577,7 +6577,7 @@
         <v>57</v>
       </c>
       <c r="E32" t="n">
-        <v>22.402930515263</v>
+        <v>22.3866374748882</v>
       </c>
     </row>
     <row r="33">
@@ -6594,7 +6594,7 @@
         <v>58</v>
       </c>
       <c r="E33" t="n">
-        <v>22.7455305016103</v>
+        <v>22.7289882976092</v>
       </c>
     </row>
     <row r="34">
@@ -6611,7 +6611,7 @@
         <v>59</v>
       </c>
       <c r="E34" t="n">
-        <v>23.2029763350841</v>
+        <v>23.186101443204</v>
       </c>
     </row>
     <row r="35">
@@ -6628,7 +6628,7 @@
         <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>22.5445680820615</v>
+        <v>22.5281720325473</v>
       </c>
     </row>
     <row r="36">
@@ -6645,7 +6645,7 @@
         <v>61</v>
       </c>
       <c r="E36" t="n">
-        <v>22.7723486928004</v>
+        <v>22.7557869846602</v>
       </c>
     </row>
     <row r="37">
@@ -6662,7 +6662,7 @@
         <v>62</v>
       </c>
       <c r="E37" t="n">
-        <v>23.0096812121402</v>
+        <v>22.9929468985314</v>
       </c>
     </row>
     <row r="38">
@@ -6679,7 +6679,7 @@
         <v>63</v>
       </c>
       <c r="E38" t="n">
-        <v>23.5492097041488</v>
+        <v>23.5320830061822</v>
       </c>
     </row>
     <row r="39">
@@ -6696,7 +6696,7 @@
         <v>64</v>
       </c>
       <c r="E39" t="n">
-        <v>24.2758225927639</v>
+        <v>24.25816744906</v>
       </c>
     </row>
     <row r="40">
@@ -6713,7 +6713,7 @@
         <v>65</v>
       </c>
       <c r="E40" t="n">
-        <v>24.419665462057</v>
+        <v>24.4019057053573</v>
       </c>
     </row>
     <row r="41">
@@ -6730,7 +6730,7 @@
         <v>66</v>
       </c>
       <c r="E41" t="n">
-        <v>24.3214656529147</v>
+        <v>24.303777314258</v>
       </c>
     </row>
     <row r="42">
@@ -6747,7 +6747,7 @@
         <v>67</v>
       </c>
       <c r="E42" t="n">
-        <v>24.871816272449</v>
+        <v>24.8537276787963</v>
       </c>
     </row>
     <row r="43">
@@ -6764,7 +6764,7 @@
         <v>68</v>
       </c>
       <c r="E43" t="n">
-        <v>25.5291194291589</v>
+        <v>25.5105527968468</v>
       </c>
     </row>
     <row r="44">
@@ -6781,7 +6781,7 @@
         <v>69</v>
       </c>
       <c r="E44" t="n">
-        <v>25.7250025403732</v>
+        <v>25.7062934476166</v>
       </c>
     </row>
     <row r="45">
@@ -6798,7 +6798,7 @@
         <v>70</v>
       </c>
       <c r="E45" t="n">
-        <v>26.2959930870007</v>
+        <v>26.276868728392</v>
       </c>
     </row>
     <row r="46">
@@ -6815,7 +6815,7 @@
         <v>71</v>
       </c>
       <c r="E46" t="n">
-        <v>27.6896277003213</v>
+        <v>27.6694897892665</v>
       </c>
     </row>
     <row r="47">
@@ -6832,7 +6832,7 @@
         <v>72</v>
       </c>
       <c r="E47" t="n">
-        <v>28.6533447255843</v>
+        <v>28.6325059294202</v>
       </c>
     </row>
     <row r="48">
@@ -6849,7 +6849,7 @@
         <v>73</v>
       </c>
       <c r="E48" t="n">
-        <v>29.6359475157134</v>
+        <v>29.6143940993383</v>
       </c>
     </row>
     <row r="49">
@@ -6866,7 +6866,7 @@
         <v>74</v>
       </c>
       <c r="E49" t="n">
-        <v>30.6506875104364</v>
+        <v>30.6283961013379</v>
       </c>
     </row>
     <row r="50">
@@ -6883,7 +6883,7 @@
         <v>75</v>
       </c>
       <c r="E50" t="n">
-        <v>31.5575950085711</v>
+        <v>31.534644030383</v>
       </c>
     </row>
     <row r="51">
@@ -6900,7 +6900,7 @@
         <v>76</v>
       </c>
       <c r="E51" t="n">
-        <v>32.0975422275036</v>
+        <v>32.0741985604291</v>
       </c>
     </row>
     <row r="52">
@@ -6917,7 +6917,7 @@
         <v>77</v>
       </c>
       <c r="E52" t="n">
-        <v>31.5648782181915</v>
+        <v>31.5419219431237</v>
       </c>
     </row>
     <row r="53">
@@ -6934,7 +6934,7 @@
         <v>78</v>
       </c>
       <c r="E53" t="n">
-        <v>33.3801799370199</v>
+        <v>33.3559034425203</v>
       </c>
     </row>
     <row r="54">
@@ -6951,7 +6951,7 @@
         <v>79</v>
       </c>
       <c r="E54" t="n">
-        <v>34.5296505924255</v>
+        <v>34.5045381192674</v>
       </c>
     </row>
     <row r="55">
@@ -6968,7 +6968,7 @@
         <v>80</v>
       </c>
       <c r="E55" t="n">
-        <v>35.025493429272</v>
+        <v>35.0000203431416</v>
       </c>
     </row>
     <row r="56">
@@ -6985,7 +6985,7 @@
         <v>81</v>
       </c>
       <c r="E56" t="n">
-        <v>35.3273484616819</v>
+        <v>35.3016558446189</v>
       </c>
     </row>
     <row r="57">
@@ -7002,7 +7002,7 @@
         <v>82</v>
       </c>
       <c r="E57" t="n">
-        <v>35.4758953972387</v>
+        <v>35.4500947460407</v>
       </c>
     </row>
     <row r="58">
@@ -7019,7 +7019,7 @@
         <v>83</v>
       </c>
       <c r="E58" t="n">
-        <v>35.4306647269067</v>
+        <v>35.4048969707417</v>
       </c>
     </row>
     <row r="59">
@@ -7036,7 +7036,7 @@
         <v>84</v>
       </c>
       <c r="E59" t="n">
-        <v>35.4424323905176</v>
+        <v>35.4166560760518</v>
       </c>
     </row>
     <row r="60">
@@ -7053,7 +7053,7 @@
         <v>85</v>
       </c>
       <c r="E60" t="n">
-        <v>36.0160913972762</v>
+        <v>35.98989787626</v>
       </c>
     </row>
     <row r="61">
@@ -7070,7 +7070,7 @@
         <v>86</v>
       </c>
       <c r="E61" t="n">
-        <v>36.7571590366622</v>
+        <v>36.7304265573628</v>
       </c>
     </row>
     <row r="62">
@@ -7087,7 +7087,7 @@
         <v>87</v>
       </c>
       <c r="E62" t="n">
-        <v>37.1312824268496</v>
+        <v>37.1042778578119</v>
       </c>
     </row>
     <row r="63">
@@ -7104,7 +7104,7 @@
         <v>88</v>
       </c>
       <c r="E63" t="n">
-        <v>35.1520912810263</v>
+        <v>35.126526123731</v>
       </c>
     </row>
     <row r="64">
@@ -7121,7 +7121,7 @@
         <v>89</v>
       </c>
       <c r="E64" t="n">
-        <v>37.0186589367089</v>
+        <v>36.991736275664</v>
       </c>
     </row>
     <row r="65">
@@ -7138,7 +7138,7 @@
         <v>90</v>
       </c>
       <c r="E65" t="n">
-        <v>37.3209789229002</v>
+        <v>37.2938363927745</v>
       </c>
     </row>
     <row r="66">
@@ -7155,7 +7155,7 @@
         <v>91</v>
       </c>
       <c r="E66" t="n">
-        <v>37.8190734917461</v>
+        <v>37.7915687110248</v>
       </c>
     </row>
     <row r="67">
@@ -7172,7 +7172,7 @@
         <v>27</v>
       </c>
       <c r="E67" t="n">
-        <v>7.74932583333333</v>
+        <v>7.74368996</v>
       </c>
     </row>
     <row r="68">
@@ -7189,7 +7189,7 @@
         <v>28</v>
       </c>
       <c r="E68" t="n">
-        <v>6.71088916666667</v>
+        <v>6.70600852</v>
       </c>
     </row>
     <row r="69">
@@ -7206,7 +7206,7 @@
         <v>29</v>
       </c>
       <c r="E69" t="n">
-        <v>6.82549083333333</v>
+        <v>6.82052684</v>
       </c>
     </row>
     <row r="70">
@@ -7223,7 +7223,7 @@
         <v>30</v>
       </c>
       <c r="E70" t="n">
-        <v>6.33530333333333</v>
+        <v>6.33069584</v>
       </c>
     </row>
     <row r="71">
@@ -7240,7 +7240,7 @@
         <v>31</v>
       </c>
       <c r="E71" t="n">
-        <v>6.16576583333333</v>
+        <v>6.16128164</v>
       </c>
     </row>
     <row r="72">
@@ -7257,7 +7257,7 @@
         <v>32</v>
       </c>
       <c r="E72" t="n">
-        <v>5.86309166666667</v>
+        <v>5.8588276</v>
       </c>
     </row>
     <row r="73">
@@ -7274,7 +7274,7 @@
         <v>33</v>
       </c>
       <c r="E73" t="n">
-        <v>5.629195</v>
+        <v>5.62510104</v>
       </c>
     </row>
     <row r="74">
@@ -7291,7 +7291,7 @@
         <v>34</v>
       </c>
       <c r="E74" t="n">
-        <v>5.22663166666667</v>
+        <v>5.22283048</v>
       </c>
     </row>
     <row r="75">
@@ -7308,7 +7308,7 @@
         <v>35</v>
       </c>
       <c r="E75" t="n">
-        <v>5.40478583333333</v>
+        <v>5.40085508</v>
       </c>
     </row>
     <row r="76">
@@ -7325,7 +7325,7 @@
         <v>36</v>
       </c>
       <c r="E76" t="n">
-        <v>5.33628333333333</v>
+        <v>5.3324024</v>
       </c>
     </row>
     <row r="77">
@@ -7342,7 +7342,7 @@
         <v>37</v>
       </c>
       <c r="E77" t="n">
-        <v>5.84022083333333</v>
+        <v>5.8359734</v>
       </c>
     </row>
     <row r="78">
@@ -7359,7 +7359,7 @@
         <v>38</v>
       </c>
       <c r="E78" t="n">
-        <v>5.6982475</v>
+        <v>5.69410332</v>
       </c>
     </row>
     <row r="79">
@@ -7376,7 +7376,7 @@
         <v>39</v>
       </c>
       <c r="E79" t="n">
-        <v>5.12182</v>
+        <v>5.11809504</v>
       </c>
     </row>
     <row r="80">
@@ -7393,7 +7393,7 @@
         <v>40</v>
       </c>
       <c r="E80" t="n">
-        <v>5.3944825</v>
+        <v>5.39055924</v>
       </c>
     </row>
     <row r="81">
@@ -7410,7 +7410,7 @@
         <v>41</v>
       </c>
       <c r="E81" t="n">
-        <v>5.24789833333333</v>
+        <v>5.24408168</v>
       </c>
     </row>
     <row r="82">
@@ -7427,7 +7427,7 @@
         <v>42</v>
       </c>
       <c r="E82" t="n">
-        <v>5.1421425</v>
+        <v>5.13840276</v>
       </c>
     </row>
     <row r="83">
@@ -7444,7 +7444,7 @@
         <v>43</v>
       </c>
       <c r="E83" t="n">
-        <v>5.06301583333333</v>
+        <v>5.05933364</v>
       </c>
     </row>
     <row r="84">
@@ -7461,7 +7461,7 @@
         <v>44</v>
       </c>
       <c r="E84" t="n">
-        <v>5.08787583333333</v>
+        <v>5.08417556</v>
       </c>
     </row>
     <row r="85">
@@ -7478,7 +7478,7 @@
         <v>45</v>
       </c>
       <c r="E85" t="n">
-        <v>5.51778333333333</v>
+        <v>5.5137704</v>
       </c>
     </row>
     <row r="86">
@@ -7495,7 +7495,7 @@
         <v>46</v>
       </c>
       <c r="E86" t="n">
-        <v>5.41699583333333</v>
+        <v>5.4130562</v>
       </c>
     </row>
     <row r="87">
@@ -7512,7 +7512,7 @@
         <v>47</v>
       </c>
       <c r="E87" t="n">
-        <v>4.69016166666667</v>
+        <v>4.68675064</v>
       </c>
     </row>
     <row r="88">
@@ -7529,7 +7529,7 @@
         <v>48</v>
       </c>
       <c r="E88" t="n">
-        <v>4.9711475</v>
+        <v>4.96753212</v>
       </c>
     </row>
     <row r="89">
@@ -7546,7 +7546,7 @@
         <v>49</v>
       </c>
       <c r="E89" t="n">
-        <v>4.833455</v>
+        <v>4.82993976</v>
       </c>
     </row>
     <row r="90">
@@ -7563,7 +7563,7 @@
         <v>50</v>
       </c>
       <c r="E90" t="n">
-        <v>4.54700583333333</v>
+        <v>4.54369892</v>
       </c>
     </row>
     <row r="91">
@@ -7580,7 +7580,7 @@
         <v>51</v>
       </c>
       <c r="E91" t="n">
-        <v>4.7884375</v>
+        <v>4.784955</v>
       </c>
     </row>
     <row r="92">
@@ -7597,7 +7597,7 @@
         <v>52</v>
       </c>
       <c r="E92" t="n">
-        <v>5.64318333333333</v>
+        <v>5.6390792</v>
       </c>
     </row>
     <row r="93">
@@ -7614,7 +7614,7 @@
         <v>53</v>
       </c>
       <c r="E93" t="n">
-        <v>5.29481333333333</v>
+        <v>5.29096256</v>
       </c>
     </row>
     <row r="94">
@@ -7631,7 +7631,7 @@
         <v>54</v>
       </c>
       <c r="E94" t="n">
-        <v>5.53120333333333</v>
+        <v>5.52718064</v>
       </c>
     </row>
     <row r="95">
@@ -7648,7 +7648,7 @@
         <v>55</v>
       </c>
       <c r="E95" t="n">
-        <v>5.34369</v>
+        <v>5.33980368</v>
       </c>
     </row>
     <row r="96">
@@ -7665,7 +7665,7 @@
         <v>56</v>
       </c>
       <c r="E96" t="n">
-        <v>5.17474833333333</v>
+        <v>5.17098488</v>
       </c>
     </row>
     <row r="97">
@@ -7682,7 +7682,7 @@
         <v>57</v>
       </c>
       <c r="E97" t="n">
-        <v>4.95694833333333</v>
+        <v>4.95334328</v>
       </c>
     </row>
     <row r="98">
@@ -7699,7 +7699,7 @@
         <v>58</v>
       </c>
       <c r="E98" t="n">
-        <v>4.9802225</v>
+        <v>4.97660052</v>
       </c>
     </row>
     <row r="99">
@@ -7716,7 +7716,7 @@
         <v>59</v>
       </c>
       <c r="E99" t="n">
-        <v>4.97360416666667</v>
+        <v>4.969987</v>
       </c>
     </row>
     <row r="100">
@@ -7733,7 +7733,7 @@
         <v>60</v>
       </c>
       <c r="E100" t="n">
-        <v>5.26183166666667</v>
+        <v>5.25800488</v>
       </c>
     </row>
     <row r="101">
@@ -7750,7 +7750,7 @@
         <v>61</v>
       </c>
       <c r="E101" t="n">
-        <v>4.97748166666667</v>
+        <v>4.97386168</v>
       </c>
     </row>
     <row r="102">
@@ -7767,7 +7767,7 @@
         <v>62</v>
       </c>
       <c r="E102" t="n">
-        <v>5.8936625</v>
+        <v>5.8893762</v>
       </c>
     </row>
     <row r="103">
@@ -7784,7 +7784,7 @@
         <v>63</v>
       </c>
       <c r="E103" t="n">
-        <v>5.43635583333333</v>
+        <v>5.43240212</v>
       </c>
     </row>
     <row r="104">
@@ -7801,7 +7801,7 @@
         <v>64</v>
       </c>
       <c r="E104" t="n">
-        <v>6.0169175</v>
+        <v>6.01254156</v>
       </c>
     </row>
     <row r="105">
@@ -7818,7 +7818,7 @@
         <v>65</v>
       </c>
       <c r="E105" t="n">
-        <v>7.41195583333333</v>
+        <v>7.40656532</v>
       </c>
     </row>
     <row r="106">
@@ -7835,7 +7835,7 @@
         <v>66</v>
       </c>
       <c r="E106" t="n">
-        <v>6.14893583333333</v>
+        <v>6.14446388</v>
       </c>
     </row>
     <row r="107">
@@ -7852,7 +7852,7 @@
         <v>67</v>
       </c>
       <c r="E107" t="n">
-        <v>6.00728333333333</v>
+        <v>6.0029144</v>
       </c>
     </row>
     <row r="108">
@@ -7869,7 +7869,7 @@
         <v>68</v>
       </c>
       <c r="E108" t="n">
-        <v>5.30107416666667</v>
+        <v>5.29721884</v>
       </c>
     </row>
     <row r="109">
@@ -7886,7 +7886,7 @@
         <v>69</v>
       </c>
       <c r="E109" t="n">
-        <v>4.76871083333333</v>
+        <v>4.76524268</v>
       </c>
     </row>
     <row r="110">
@@ -7903,7 +7903,7 @@
         <v>70</v>
       </c>
       <c r="E110" t="n">
-        <v>5.13184833333333</v>
+        <v>5.12811608</v>
       </c>
     </row>
     <row r="111">
@@ -7920,7 +7920,7 @@
         <v>71</v>
       </c>
       <c r="E111" t="n">
-        <v>6.08010333333333</v>
+        <v>6.07568144</v>
       </c>
     </row>
     <row r="112">
@@ -7937,7 +7937,7 @@
         <v>72</v>
       </c>
       <c r="E112" t="n">
-        <v>5.40792083333333</v>
+        <v>5.4039878</v>
       </c>
     </row>
     <row r="113">
@@ -7954,7 +7954,7 @@
         <v>73</v>
       </c>
       <c r="E113" t="n">
-        <v>4.89454166666667</v>
+        <v>4.890982</v>
       </c>
     </row>
     <row r="114">
@@ -7971,7 +7971,7 @@
         <v>74</v>
       </c>
       <c r="E114" t="n">
-        <v>5.33602666666667</v>
+        <v>5.33214592</v>
       </c>
     </row>
     <row r="115">
@@ -7988,7 +7988,7 @@
         <v>75</v>
       </c>
       <c r="E115" t="n">
-        <v>4.59792666666667</v>
+        <v>4.59458272</v>
       </c>
     </row>
     <row r="116">
@@ -8005,7 +8005,7 @@
         <v>76</v>
       </c>
       <c r="E116" t="n">
-        <v>4.8838625</v>
+        <v>4.8803106</v>
       </c>
     </row>
     <row r="117">
@@ -8022,7 +8022,7 @@
         <v>77</v>
       </c>
       <c r="E117" t="n">
-        <v>5.27781833333333</v>
+        <v>5.27397992</v>
       </c>
     </row>
     <row r="118">
@@ -8039,7 +8039,7 @@
         <v>78</v>
       </c>
       <c r="E118" t="n">
-        <v>5.49190583333333</v>
+        <v>5.48791172</v>
       </c>
     </row>
     <row r="119">
@@ -8056,7 +8056,7 @@
         <v>79</v>
       </c>
       <c r="E119" t="n">
-        <v>5.28210833333333</v>
+        <v>5.2782668</v>
       </c>
     </row>
     <row r="120">
@@ -8073,7 +8073,7 @@
         <v>80</v>
       </c>
       <c r="E120" t="n">
-        <v>5.6560075</v>
+        <v>5.65189404</v>
       </c>
     </row>
     <row r="121">
@@ -8090,7 +8090,7 @@
         <v>81</v>
       </c>
       <c r="E121" t="n">
-        <v>5.11987666666667</v>
+        <v>5.11615312</v>
       </c>
     </row>
     <row r="122">
@@ -8107,7 +8107,7 @@
         <v>82</v>
       </c>
       <c r="E122" t="n">
-        <v>5.40012</v>
+        <v>5.39619264</v>
       </c>
     </row>
     <row r="123">
@@ -8124,7 +8124,7 @@
         <v>83</v>
       </c>
       <c r="E123" t="n">
-        <v>5.5356125</v>
+        <v>5.5315866</v>
       </c>
     </row>
     <row r="124">
@@ -8141,7 +8141,7 @@
         <v>84</v>
       </c>
       <c r="E124" t="n">
-        <v>4.40946</v>
+        <v>4.40625312</v>
       </c>
     </row>
     <row r="125">
@@ -8158,7 +8158,7 @@
         <v>85</v>
       </c>
       <c r="E125" t="n">
-        <v>4.23410166666667</v>
+        <v>4.23102232</v>
       </c>
     </row>
     <row r="126">
@@ -8175,7 +8175,7 @@
         <v>86</v>
       </c>
       <c r="E126" t="n">
-        <v>3.84751583333333</v>
+        <v>3.84471764</v>
       </c>
     </row>
     <row r="127">
@@ -8192,7 +8192,7 @@
         <v>87</v>
       </c>
       <c r="E127" t="n">
-        <v>3.7895</v>
+        <v>3.786744</v>
       </c>
     </row>
     <row r="128">
@@ -8209,7 +8209,7 @@
         <v>88</v>
       </c>
       <c r="E128" t="n">
-        <v>3.44149666666667</v>
+        <v>3.43899376</v>
       </c>
     </row>
     <row r="129">
@@ -8226,7 +8226,7 @@
         <v>89</v>
       </c>
       <c r="E129" t="n">
-        <v>3.555365</v>
+        <v>3.55277928</v>
       </c>
     </row>
     <row r="130">
@@ -8243,7 +8243,7 @@
         <v>90</v>
       </c>
       <c r="E130" t="n">
-        <v>3.54361333333333</v>
+        <v>3.54103616</v>
       </c>
     </row>
     <row r="131">
@@ -8260,7 +8260,7 @@
         <v>91</v>
       </c>
       <c r="E131" t="n">
-        <v>3.62754333333333</v>
+        <v>3.62490512</v>
       </c>
     </row>
     <row r="132">

--- a/results/ghg_emissions_co2e_2025.xlsx
+++ b/results/ghg_emissions_co2e_2025.xlsx
@@ -5910,7 +5910,7 @@
         <v>2018</v>
       </c>
       <c r="B270" t="n">
-        <v>1.68435257202591</v>
+        <v>1.67739511265847</v>
       </c>
       <c r="C270" t="n">
         <v>2.814308679</v>
@@ -5930,7 +5930,7 @@
         <v>2019</v>
       </c>
       <c r="B271" t="n">
-        <v>1.73907398402602</v>
+        <v>1.73884589137722</v>
       </c>
       <c r="C271" t="n">
         <v>2.819371737</v>
@@ -5950,7 +5950,7 @@
         <v>2020</v>
       </c>
       <c r="B272" t="n">
-        <v>1.78725447483064</v>
+        <v>1.79398384154928</v>
       </c>
       <c r="C272" t="n">
         <v>2.853203808</v>
@@ -6010,7 +6010,7 @@
         <v>2023</v>
       </c>
       <c r="B275" t="n">
-        <v>1.5696262934027</v>
+        <v>1.8687391979819</v>
       </c>
       <c r="C275" t="n">
         <v>2.912036946</v>
